--- a/docs/platform/PLATFORM_ROLE_NAV_DUPLICATION_MATRIX.xlsx
+++ b/docs/platform/PLATFORM_ROLE_NAV_DUPLICATION_MATRIX.xlsx
@@ -15,11 +15,12 @@
     <sheet name="Tabbed Pages (intentional)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Dashboards" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Unused Endpoints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Orphans" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Persona Seed Gap" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Decision Table" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Ranked PR List" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Out of Scope (PR-0)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Orphans (split)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Forbidden-Visible (deferred)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Persona Seed Gap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Decision Table" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ranked PR List" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Out of Scope (PR-0)" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -975,6 +976,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>status in PR-0</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>ملاحظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>غير محسوم نهائيًا — مرحَّل لـPR-6/PR-8</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>القياس يتطلب login لكل دور قياسي ثم محاولة فتح كل path يراه في nav. اليوم 5 من 10 personas لا users لها في الـtenant (Seed Gap). الـ`?` في Summary لا يعني «صفر».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>ما الذي يحوّله إلى رقم نهائي؟</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>PR-6 من الموجة 2 (سدّ seed gap) + PR-8 (الرحلة الشاملة عبر 10 personas × 12 dashboard × 472 nav).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ما الذي تمكّنت الرحلة READ-ONLY من قياسه اليوم؟</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>4 personas جاهزة (owner / hr_manager / department_manager / payroll_officer). الإشارة الواضحة من نتائجها: تباين تسميات modules بين /auth/me وrequireModule (§8).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1211,7 +1278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1565,7 +1632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1838,7 +1905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60956,96 +61023,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
           <t>path</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>page_file</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>verdict (suggested)</t>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>owning PR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>/admin/attendance-categories</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>pages/admin/attendance-categories</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>merge with /hr/attendance-categories (see Cross-Module Duplicates)</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>6.A actual orphan</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr"/>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>no path qualifies after de-duplication / deep-link / back-compat filtering</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>/admin/scoring-weights</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>pages/admin/scoring-weights</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>merge with /hr/scoring-weights (see Cross-Module Duplicates)</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>6.B deep-link-only</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>/umrah/commission-plans/new</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>pages/umrah/commission-plan-editor</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>called from /umrah/commission-plans list (zر «جديد»); standard /create pattern; do NOT add to nav</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PR-4 (doc only)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
+          <t>6.C back-compat</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
           <t>/my/work-queue</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>pages/my/work-queue</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>deprecated by /work-inbox? — confirm with PR-5 author</t>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>superseded by /work-inbox (PR-5 of #2077); recommend redirect + later removal</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>PR-4 (redirect)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
+          <t>6.D nav-add</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
           <t>/umrah/transport-requests</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>pages/umrah/transport-requests</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>expose under umrah → transport section</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>add nav item under «العمرة → النقل»</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>PR-4 (nav-add)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>6.E orphan + duplicate</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>/admin/attendance-categories</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>pages/admin/attendance-categories</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>resolved by deduplicating with /hr/attendance-categories (canonical decision in §4)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PR-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>6.E orphan + duplicate</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>/admin/scoring-weights</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>pages/admin/scoring-weights</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>resolved by deduplicating with /hr/scoring-weights (canonical decision in §4)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>PR-3</t>
         </is>
       </c>
     </row>
